--- a/output/lgbm_reg/02_feature_selection/特征筛选报告.xlsx
+++ b/output/lgbm_reg/02_feature_selection/特征筛选报告.xlsx
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.021</v>
+        <v>0.0187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0564</v>
+        <v>0.0494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0604</v>
+        <v>0.0283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0372</v>
+        <v>0.0242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0667</v>
+        <v>0.0064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0581</v>
+        <v>0.0235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.021</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="3">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0604</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="4">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0372</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="5">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0667</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="6">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0581</v>
+        <v>0.0235</v>
       </c>
     </row>
   </sheetData>
